--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-17).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-17).xlsx
@@ -915,66 +915,66 @@
   </si>
   <si>
     <t>215
-145</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>R$ 1.459.738,98</t>
-  </si>
-  <si>
-    <t>R$ 9.297,70
-R$ 9.535,62</t>
-  </si>
-  <si>
-    <t>(8.6%)
-(6.3%)</t>
-  </si>
-  <si>
-    <t>98.0</t>
-  </si>
-  <si>
-    <t>(11.1%)</t>
-  </si>
-  <si>
-    <t>64.8%</t>
-  </si>
-  <si>
-    <t>21.5%</t>
-  </si>
-  <si>
-    <t>2.5%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>27.8</t>
-  </si>
-  <si>
-    <t>63.2%</t>
-  </si>
-  <si>
-    <t>11.7%</t>
+170</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 1.719.893,36</t>
+  </si>
+  <si>
+    <t>R$ 9.347,25
+R$ 9.586,69</t>
+  </si>
+  <si>
+    <t>(7.5%)
+(5.1%)</t>
+  </si>
+  <si>
+    <t>98.4</t>
+  </si>
+  <si>
+    <t>(10.2%)</t>
+  </si>
+  <si>
+    <t>59.1%</t>
+  </si>
+  <si>
+    <t>17.6%</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>28.0</t>
+  </si>
+  <si>
+    <t>62.7%</t>
+  </si>
+  <si>
+    <t>12.4%</t>
   </si>
   <si>
     <t>6.0</t>
   </si>
   <si>
-    <t>6.8</t>
-  </si>
-  <si>
-    <t>12.8</t>
-  </si>
-  <si>
-    <t>19.6</t>
-  </si>
-  <si>
-    <t>67.9%</t>
-  </si>
-  <si>
-    <t>-R$ 32.399,40</t>
+    <t>6.9</t>
+  </si>
+  <si>
+    <t>13.1</t>
+  </si>
+  <si>
+    <t>19.8</t>
+  </si>
+  <si>
+    <t>67.1%</t>
+  </si>
+  <si>
+    <t>-R$ 38.719,44</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2349,10 +2349,10 @@
         <v>0.21052631578947367</v>
       </c>
       <c r="T8" s="6">
-        <v>0.32207603861261358</v>
+        <v>0.3707568782507395</v>
       </c>
       <c r="U8" s="6">
-        <v>-0.015456928920050754</v>
+        <v>0.033223910718075081</v>
       </c>
       <c r="V8" s="6">
         <v>0.022369071798847166</v>
@@ -3028,7 +3028,9 @@
       <c r="AB13" s="8">
         <v>5.3287702380952382</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>21.395047999999999</v>
+      </c>
       <c r="AD13" s="8">
         <v>28.557738095238093</v>
       </c>
@@ -3288,7 +3290,9 @@
       <c r="AB15" s="8">
         <v>3.0214743589743591</v>
       </c>
-      <c r="AC15" s="8"/>
+      <c r="AC15" s="8">
+        <v>11.022627</v>
+      </c>
       <c r="AD15" s="8">
         <v>17.889098742138366</v>
       </c>
@@ -3417,7 +3421,9 @@
       <c r="AB16" s="8">
         <v>35.655000000000001</v>
       </c>
-      <c r="AC16" s="8"/>
+      <c r="AC16" s="8">
+        <v>45.266309</v>
+      </c>
       <c r="AD16" s="8">
         <v>50.345835000000001</v>
       </c>
@@ -3922,7 +3928,7 @@
         <v>0.00999047247568563</v>
       </c>
       <c r="W20" s="6">
-        <v>-0.0071255011541732482</v>
+        <v>-0.0069501904439144262</v>
       </c>
       <c r="X20" s="8">
         <v>23.886069402985072</v>
@@ -4834,7 +4840,7 @@
         <v>-226.90000000000001</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -4873,7 +4879,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4909,25 +4915,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>8416.5300000000007</v>
+      </c>
+      <c r="P28" s="5">
+        <v>8416.5300000000007</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>-0.074811753196073472</v>
+      </c>
+      <c r="R28" s="7">
+        <v>84</v>
+      </c>
+      <c r="S28" s="6">
+        <v>-0.16831683168316836</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.00026023788901126713</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.31035827116400699</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.073530124647568529</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.064967213329008511</v>
+      </c>
+      <c r="X28" s="8">
+        <v>24.911437254901962</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>2.2400402439024392</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>7.2650333333333332</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>9.4490180000000006</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>16.399672549019606</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.76470588235294112</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-829.27999999999997</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -5359,7 +5401,7 @@
         <v>19552</v>
       </c>
       <c r="B32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C32" s="4">
         <v>44</v>
@@ -5395,25 +5437,61 @@
       <c t="s" r="N32" s="4">
         <v>52</v>
       </c>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="7"/>
-      <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="6"/>
-      <c r="W32" s="6"/>
-      <c r="X32" s="8"/>
-      <c r="Y32" s="6"/>
-      <c r="Z32" s="6"/>
-      <c r="AA32" s="8"/>
-      <c r="AB32" s="8"/>
-      <c r="AC32" s="8"/>
-      <c r="AD32" s="8"/>
-      <c r="AE32" s="6"/>
+      <c r="O32" s="5">
+        <v>19610.200000000001</v>
+      </c>
+      <c r="P32" s="5">
+        <v>19610.200000000001</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>-0.13054967233008086</v>
+      </c>
+      <c r="R32" s="7">
+        <v>183</v>
+      </c>
+      <c r="S32" s="6">
+        <v>-0.1830357142857143</v>
+      </c>
+      <c r="T32" s="6">
+        <v>0.24229754923458197</v>
+      </c>
+      <c r="U32" s="6">
+        <v>-0.044860664348145347</v>
+      </c>
+      <c r="V32" s="6">
+        <v>0.028273449531366329</v>
+      </c>
+      <c r="W32" s="6">
+        <v>0.015607591967445511</v>
+      </c>
+      <c r="X32" s="8">
+        <v>21.103914765100669</v>
+      </c>
+      <c r="Y32" s="6">
+        <v>0.91946308724832215</v>
+      </c>
+      <c r="Z32" s="6">
+        <v>0.0067114093959731542</v>
+      </c>
+      <c r="AA32" s="8">
+        <v>2.1306774725274726</v>
+      </c>
+      <c r="AB32" s="8">
+        <v>3.7807604026845638</v>
+      </c>
+      <c r="AC32" s="8">
+        <v>5.8517890000000001</v>
+      </c>
+      <c r="AD32" s="8">
+        <v>11.813870469798657</v>
+      </c>
+      <c r="AE32" s="6">
+        <v>0.94630872483221473</v>
+      </c>
       <c r="AF32" s="9"/>
-      <c r="AG32" s="5"/>
+      <c r="AG32" s="5">
+        <v>0</v>
+      </c>
       <c r="AH32" s="10">
         <v>4</v>
       </c>
@@ -5454,7 +5532,7 @@
         <v>19553</v>
       </c>
       <c r="B33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C33" s="4">
         <v>44</v>
@@ -5488,25 +5566,61 @@
       <c t="s" r="N33" s="4">
         <v>52</v>
       </c>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="8"/>
-      <c r="Y33" s="6"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="8"/>
-      <c r="AB33" s="8"/>
-      <c r="AC33" s="8"/>
-      <c r="AD33" s="8"/>
-      <c r="AE33" s="6"/>
+      <c r="O33" s="5">
+        <v>14252.049999999999</v>
+      </c>
+      <c r="P33" s="5">
+        <v>14252.049999999999</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>0.57505929107108522</v>
+      </c>
+      <c r="R33" s="7">
+        <v>118</v>
+      </c>
+      <c r="S33" s="6">
+        <v>0.37209302325581395</v>
+      </c>
+      <c r="T33" s="6">
+        <v>0.27008349676011523</v>
+      </c>
+      <c r="U33" s="6">
+        <v>-0.036144028402931509</v>
+      </c>
+      <c r="V33" s="6">
+        <v>0.026015099582165375</v>
+      </c>
+      <c r="W33" s="6">
+        <v>0.0097276181321283607</v>
+      </c>
+      <c r="X33" s="8">
+        <v>26.896527777777777</v>
+      </c>
+      <c r="Y33" s="6">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="Z33" s="6">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="AA33" s="8">
+        <v>4.5730228813559322</v>
+      </c>
+      <c r="AB33" s="8">
+        <v>5.9168986111111117</v>
+      </c>
+      <c r="AC33" s="8">
+        <v>10.792592000000001</v>
+      </c>
+      <c r="AD33" s="8">
+        <v>17.744444444444444</v>
+      </c>
+      <c r="AE33" s="6">
+        <v>0.76388888888888884</v>
+      </c>
       <c r="AF33" s="9"/>
-      <c r="AG33" s="5"/>
+      <c r="AG33" s="5">
+        <v>0</v>
+      </c>
       <c r="AH33" s="10">
         <v>5</v>
       </c>
@@ -5625,7 +5739,9 @@
       <c r="AB34" s="8">
         <v>1.7318681318681317</v>
       </c>
-      <c r="AC34" s="8"/>
+      <c r="AC34" s="8">
+        <v>6.6383190000000001</v>
+      </c>
       <c r="AD34" s="8">
         <v>12.473476344086022</v>
       </c>
@@ -5730,10 +5846,10 @@
         <v>-0.10769230769230764</v>
       </c>
       <c r="T35" s="6">
-        <v>0.30760980693059037</v>
+        <v>2.1987565756274927</v>
       </c>
       <c r="U35" s="6">
-        <v>0.00053232339990184072</v>
+        <v>1.8916790920968043</v>
       </c>
       <c r="V35" s="6">
         <v>0.054068248273573753</v>
@@ -6204,7 +6320,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6240,25 +6356,61 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="O39" s="5">
+        <v>11867.15</v>
+      </c>
+      <c r="P39" s="5">
+        <v>11867.15</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0.22082735803830622</v>
+      </c>
+      <c r="R39" s="7">
+        <v>133</v>
+      </c>
+      <c r="S39" s="6">
+        <v>0.15652173913043477</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.29022125784202613</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.023318218780414842</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.062202508605688822</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.039443885010301549</v>
+      </c>
+      <c r="X39" s="8">
+        <v>26.162156470588236</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>0.97647058823529409</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0.082352941176470587</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>2.8129921259842519</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>8.6369914634146348</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>11.48052</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>18.991568235294118</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.76470588235294112</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6377,7 +6529,9 @@
       <c r="AB40" s="8">
         <v>9.0472972972972965</v>
       </c>
-      <c r="AC40" s="8"/>
+      <c r="AC40" s="8">
+        <v>13.838246</v>
+      </c>
       <c r="AD40" s="8">
         <v>20.656989247311827</v>
       </c>
@@ -6559,7 +6713,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6595,25 +6749,57 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
+      <c r="O42" s="5">
+        <v>6897.4300000000003</v>
+      </c>
+      <c r="P42" s="5">
+        <v>6897.4300000000003</v>
+      </c>
       <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
+      <c r="R42" s="7">
+        <v>79</v>
+      </c>
       <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="T42" s="6">
+        <v>0.37759819237020165</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.056250965939487606</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.054199027753815548</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.020264649296912039</v>
+      </c>
+      <c r="X42" s="8">
+        <v>23.64761836734694</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.83673469387755106</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.4069259740259739</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>4.5826395833333331</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>10.854638</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>17.703402040816325</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.89795918367346939</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -6654,7 +6840,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>44</v>
@@ -6690,25 +6876,61 @@
       <c t="s" r="N43" s="4">
         <v>52</v>
       </c>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="8"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="8"/>
-      <c r="AB43" s="8"/>
-      <c r="AC43" s="8"/>
-      <c r="AD43" s="8"/>
-      <c r="AE43" s="6"/>
+      <c r="O43" s="5">
+        <v>11426.860000000001</v>
+      </c>
+      <c r="P43" s="5">
+        <v>11426.860000000001</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>0.070841127100568668</v>
+      </c>
+      <c r="R43" s="7">
+        <v>97</v>
+      </c>
+      <c r="S43" s="6">
+        <v>-0.15652173913043477</v>
+      </c>
+      <c r="T43" s="6">
+        <v>2.2079556413572934E-05</v>
+      </c>
+      <c r="U43" s="6">
+        <v>-0.30125841219722649</v>
+      </c>
+      <c r="V43" s="6">
+        <v>0.013286458397144971</v>
+      </c>
+      <c r="W43" s="6">
+        <v>-0.001512882804199929</v>
+      </c>
+      <c r="X43" s="8">
+        <v>36.683561643835617</v>
+      </c>
+      <c r="Y43" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z43" s="6">
+        <v>0.26027397260273971</v>
+      </c>
+      <c r="AA43" s="8">
+        <v>6.6395185567010317</v>
+      </c>
+      <c r="AB43" s="8">
+        <v>11.194676388888888</v>
+      </c>
+      <c r="AC43" s="8">
+        <v>18.381119000000002</v>
+      </c>
+      <c r="AD43" s="8">
+        <v>25.057534246575344</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>0.16438356164383561</v>
+      </c>
       <c r="AF43" s="9"/>
-      <c r="AG43" s="5"/>
+      <c r="AG43" s="5">
+        <v>0</v>
+      </c>
       <c r="AH43" s="10">
         <v>1</v>
       </c>
@@ -7529,7 +7751,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7565,25 +7787,61 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="O50" s="5">
+        <v>8260.7600000000002</v>
+      </c>
+      <c r="P50" s="5">
+        <v>8260.7600000000002</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>-0.20252003653010353</v>
+      </c>
+      <c r="R50" s="7">
+        <v>94</v>
+      </c>
+      <c r="S50" s="6">
+        <v>-0.24193548387096775</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.19119024157583564</v>
+      </c>
+      <c r="U50" s="6">
+        <v>-0.12087063417893752</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.065560009006435244</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.034260225451411247</v>
+      </c>
+      <c r="X50" s="8">
+        <v>22.465607936507936</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>0.96825396825396826</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>2.9688402173913047</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>5.1470435483870967</v>
+      </c>
+      <c r="AC50" s="8">
+        <v>8.2074590000000001</v>
+      </c>
+      <c r="AD50" s="8">
+        <v>15.87063492063492</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.92063492063492058</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -7850,7 +8108,7 @@
         <v>19607</v>
       </c>
       <c r="B53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C53" s="4">
         <v>44</v>
@@ -7884,25 +8142,61 @@
       <c t="s" r="N53" s="4">
         <v>52</v>
       </c>
-      <c r="O53" s="5"/>
-      <c r="P53" s="5"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="7"/>
-      <c r="S53" s="6"/>
-      <c r="T53" s="6"/>
-      <c r="U53" s="6"/>
-      <c r="V53" s="6"/>
-      <c r="W53" s="6"/>
-      <c r="X53" s="8"/>
-      <c r="Y53" s="6"/>
-      <c r="Z53" s="6"/>
-      <c r="AA53" s="8"/>
-      <c r="AB53" s="8"/>
-      <c r="AC53" s="8"/>
-      <c r="AD53" s="8"/>
-      <c r="AE53" s="6"/>
+      <c r="O53" s="5">
+        <v>9177.5</v>
+      </c>
+      <c r="P53" s="5">
+        <v>9177.5</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>0.89495223130496182</v>
+      </c>
+      <c r="R53" s="7">
+        <v>97</v>
+      </c>
+      <c r="S53" s="6">
+        <v>0.42647058823529416</v>
+      </c>
+      <c r="T53" s="6">
+        <v>0.25462021247616456</v>
+      </c>
+      <c r="U53" s="6">
+        <v>-0.079456605829474253</v>
+      </c>
+      <c r="V53" s="6">
+        <v>0.031053718332879322</v>
+      </c>
+      <c r="W53" s="6">
+        <v>0.011872023971669844</v>
+      </c>
+      <c r="X53" s="8">
+        <v>22.548214285714288</v>
+      </c>
+      <c r="Y53" s="6">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="Z53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="8">
+        <v>2.6807021052631579</v>
+      </c>
+      <c r="AB53" s="8">
+        <v>2.9750000000000001</v>
+      </c>
+      <c r="AC53" s="8">
+        <v>5.7491070000000004</v>
+      </c>
+      <c r="AD53" s="8">
+        <v>12.675892857142857</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>0.8928571428571429</v>
+      </c>
       <c r="AF53" s="9"/>
-      <c r="AG53" s="5"/>
+      <c r="AG53" s="5">
+        <v>-168.80000000000001</v>
+      </c>
       <c r="AH53" s="10">
         <v>3</v>
       </c>
@@ -8074,7 +8368,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -8110,25 +8404,61 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="O55" s="5">
+        <v>11267.07</v>
+      </c>
+      <c r="P55" s="5">
+        <v>11267.07</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>0.1272469512896679</v>
+      </c>
+      <c r="R55" s="7">
+        <v>129</v>
+      </c>
+      <c r="S55" s="6">
+        <v>0.20560747663551404</v>
+      </c>
+      <c r="T55" s="6">
+        <v>7.9878797238323721E-06</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.31833830800731688</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.063222204175530997</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.03851835481629208</v>
+      </c>
+      <c r="X55" s="8">
+        <v>39.091941758241759</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.065217391304347824</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.45054945054945056</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>3.3671719696969697</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>10.874818478260869</v>
+      </c>
+      <c r="AC55" s="8">
+        <v>14.093256999999999</v>
+      </c>
+      <c r="AD55" s="8">
+        <v>20.94891304347826</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.17582417582417584</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -8245,7 +8575,9 @@
       <c r="AB56" s="8">
         <v>5.3634782608695648</v>
       </c>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="8">
+        <v>11.978873</v>
+      </c>
       <c r="AD56" s="8">
         <v>20.144349999999999</v>
       </c>
@@ -8374,7 +8706,9 @@
       <c r="AB57" s="8">
         <v>4.1307692307692303</v>
       </c>
-      <c r="AC57" s="8"/>
+      <c r="AC57" s="8">
+        <v>10.674572</v>
+      </c>
       <c r="AD57" s="8">
         <v>17.619444871794872</v>
       </c>
@@ -10040,7 +10374,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -10074,25 +10408,61 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
-      <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="O71" s="5">
+        <v>11262.91</v>
+      </c>
+      <c r="P71" s="5">
+        <v>11262.91</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>-0.049836126425193861</v>
+      </c>
+      <c r="R71" s="7">
+        <v>130</v>
+      </c>
+      <c r="S71" s="6">
+        <v>-0.0076335877862595547</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0.31413334564513079</v>
+      </c>
+      <c r="U71" s="6">
+        <v>0.011202753107323063</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.039820614743436643</v>
+      </c>
+      <c r="W71" s="6">
+        <v>0.013748311937145907</v>
+      </c>
+      <c r="X71" s="8">
+        <v>21.624657534246573</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>0.86301369863013699</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0.041095890410958902</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>3.1278648437499998</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>3.5029411764705882</v>
+      </c>
+      <c r="AC71" s="8">
+        <v>6.4891629999999996</v>
+      </c>
+      <c r="AD71" s="8">
+        <v>13.823972602739726</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.86301369863013699</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>-116.8</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -10482,7 +10852,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10518,25 +10888,61 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="O75" s="5">
+        <v>7619.3500000000004</v>
+      </c>
+      <c r="P75" s="5">
+        <v>7619.3500000000004</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>-0.28776344250863262</v>
+      </c>
+      <c r="R75" s="7">
+        <v>78</v>
+      </c>
+      <c r="S75" s="6">
+        <v>-0.29090909090909089</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.32067564818521266</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.039418519952489385</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.021598102200318926</v>
+      </c>
+      <c r="X75" s="8">
+        <v>24.522648717948716</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>5.5681628205128204</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>7.2692973684210527</v>
+      </c>
+      <c r="AC75" s="8">
+        <v>12.377630999999999</v>
+      </c>
+      <c r="AD75" s="8">
+        <v>18.998289743589744</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.79487179487179482</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-399.80000000000001</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10577,7 +10983,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10611,25 +11017,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>9877.0400000000009</v>
+      </c>
+      <c r="P76" s="5">
+        <v>9877.0400000000009</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.16692757182764062</v>
+      </c>
+      <c r="R76" s="7">
+        <v>109</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.1484375</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.21244738302163396</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.18411474490333135</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.038675301507334177</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.022536863270777478</v>
+      </c>
+      <c r="X76" s="8">
+        <v>39.95392156862745</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.47058823529411764</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>7.0663716814159292</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>13.754901960784315</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>20.772162000000002</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>29.334936538461537</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.31372549019607843</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-478.18000000000001</v>
+      </c>
       <c r="AH76" s="10">
         <v>1</v>
       </c>
@@ -10875,7 +11317,9 @@
       <c r="AB78" s="8">
         <v>11.170412359550562</v>
       </c>
-      <c r="AC78" s="8"/>
+      <c r="AC78" s="8">
+        <v>14.377632999999999</v>
+      </c>
       <c r="AD78" s="8">
         <v>22.33820224719101</v>
       </c>
@@ -11670,7 +12114,7 @@
         <v>19687</v>
       </c>
       <c r="B85" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C85" s="4">
         <v>44</v>
@@ -11706,25 +12150,61 @@
       <c t="s" r="N85" s="4">
         <v>52</v>
       </c>
-      <c r="O85" s="5"/>
-      <c r="P85" s="5"/>
-      <c r="Q85" s="6"/>
-      <c r="R85" s="7"/>
-      <c r="S85" s="6"/>
-      <c r="T85" s="6"/>
-      <c r="U85" s="6"/>
-      <c r="V85" s="6"/>
-      <c r="W85" s="6"/>
-      <c r="X85" s="8"/>
-      <c r="Y85" s="6"/>
-      <c r="Z85" s="6"/>
-      <c r="AA85" s="8"/>
-      <c r="AB85" s="8"/>
-      <c r="AC85" s="8"/>
-      <c r="AD85" s="8"/>
-      <c r="AE85" s="6"/>
+      <c r="O85" s="5">
+        <v>11344.75</v>
+      </c>
+      <c r="P85" s="5">
+        <v>11344.75</v>
+      </c>
+      <c r="Q85" s="6">
+        <v>0.38280120621439306</v>
+      </c>
+      <c r="R85" s="7">
+        <v>142</v>
+      </c>
+      <c r="S85" s="6">
+        <v>0.36538461538461542</v>
+      </c>
+      <c r="T85" s="6">
+        <v>0</v>
+      </c>
+      <c r="U85" s="6">
+        <v>-0.270860089468697</v>
+      </c>
+      <c r="V85" s="6">
+        <v>0.0089477070891822216</v>
+      </c>
+      <c r="W85" s="6">
+        <v>0.0052587760858546903</v>
+      </c>
+      <c r="X85" s="8">
+        <v>76.344793749999994</v>
+      </c>
+      <c r="Y85" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z85" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="AA85" s="8">
+        <v>7.5879940677966102</v>
+      </c>
+      <c r="AB85" s="8">
+        <v>55.169999999999995</v>
+      </c>
+      <c r="AC85" s="8">
+        <v>62.533541</v>
+      </c>
+      <c r="AD85" s="8">
+        <v>65.696875000000006</v>
+      </c>
+      <c r="AE85" s="6">
+        <v>0.0625</v>
+      </c>
       <c r="AF85" s="9"/>
-      <c r="AG85" s="5"/>
+      <c r="AG85" s="5">
+        <v>-1166.4000000000001</v>
+      </c>
       <c r="AH85" s="10">
         <v>3</v>
       </c>
@@ -13309,7 +13789,9 @@
       <c r="AB98" s="8">
         <v>6.1000000000000005</v>
       </c>
-      <c r="AC98" s="8"/>
+      <c r="AC98" s="8">
+        <v>12.991472</v>
+      </c>
       <c r="AD98" s="8">
         <v>19.008139534883721</v>
       </c>
@@ -13712,7 +14194,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -14592,7 +15074,7 @@
         <v>19730</v>
       </c>
       <c r="B109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C109" s="4">
         <v>44</v>
@@ -14626,25 +15108,61 @@
       <c t="s" r="N109" s="4">
         <v>52</v>
       </c>
-      <c r="O109" s="5"/>
-      <c r="P109" s="5"/>
-      <c r="Q109" s="6"/>
-      <c r="R109" s="7"/>
-      <c r="S109" s="6"/>
-      <c r="T109" s="6"/>
-      <c r="U109" s="6"/>
-      <c r="V109" s="6"/>
-      <c r="W109" s="6"/>
-      <c r="X109" s="8"/>
-      <c r="Y109" s="6"/>
-      <c r="Z109" s="6"/>
-      <c r="AA109" s="8"/>
-      <c r="AB109" s="8"/>
-      <c r="AC109" s="8"/>
-      <c r="AD109" s="8"/>
-      <c r="AE109" s="6"/>
+      <c r="O109" s="5">
+        <v>13953.41</v>
+      </c>
+      <c r="P109" s="5">
+        <v>13953.41</v>
+      </c>
+      <c r="Q109" s="6">
+        <v>0.2348390853627238</v>
+      </c>
+      <c r="R109" s="7">
+        <v>149</v>
+      </c>
+      <c r="S109" s="6">
+        <v>0.15503875968992253</v>
+      </c>
+      <c r="T109" s="6">
+        <v>-0.26769943691183734</v>
+      </c>
+      <c r="U109" s="6">
+        <v>-0.60273796871159091</v>
+      </c>
+      <c r="V109" s="6">
+        <v>0.027308880051542958</v>
+      </c>
+      <c r="W109" s="6">
+        <v>0.010424118548799183</v>
+      </c>
+      <c r="X109" s="8">
+        <v>38.339655172413792</v>
+      </c>
+      <c r="Y109" s="6">
+        <v>0.37931034482758619</v>
+      </c>
+      <c r="Z109" s="6">
+        <v>0.44827586206896552</v>
+      </c>
+      <c r="AA109" s="8">
+        <v>3.6132677631578942</v>
+      </c>
+      <c r="AB109" s="8">
+        <v>19.647127586206896</v>
+      </c>
+      <c r="AC109" s="8">
+        <v>23.500771</v>
+      </c>
+      <c r="AD109" s="8">
+        <v>31.491379310344829</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>0.31034482758620691</v>
+      </c>
       <c r="AF109" s="9"/>
-      <c r="AG109" s="5"/>
+      <c r="AG109" s="5">
+        <v>0</v>
+      </c>
       <c r="AH109" s="10">
         <v>2</v>
       </c>
@@ -15441,7 +15959,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>14.981680000000001</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -17519,7 +18039,9 @@
       <c r="AB132" s="8">
         <v>8.2825873134328365</v>
       </c>
-      <c r="AC132" s="8"/>
+      <c r="AC132" s="8">
+        <v>12.565557999999999</v>
+      </c>
       <c r="AD132" s="8">
         <v>18.141787681159418</v>
       </c>
@@ -18223,7 +18745,7 @@
         <v>19788</v>
       </c>
       <c r="B138" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C138" s="4">
         <v>44</v>
@@ -18257,25 +18779,61 @@
       <c t="s" r="N138" s="4">
         <v>52</v>
       </c>
-      <c r="O138" s="5"/>
-      <c r="P138" s="5"/>
-      <c r="Q138" s="6"/>
-      <c r="R138" s="7"/>
-      <c r="S138" s="6"/>
-      <c r="T138" s="6"/>
-      <c r="U138" s="6"/>
-      <c r="V138" s="6"/>
-      <c r="W138" s="6"/>
-      <c r="X138" s="8"/>
-      <c r="Y138" s="6"/>
-      <c r="Z138" s="6"/>
-      <c r="AA138" s="8"/>
-      <c r="AB138" s="8"/>
-      <c r="AC138" s="8"/>
-      <c r="AD138" s="8"/>
-      <c r="AE138" s="6"/>
+      <c r="O138" s="5">
+        <v>23095.919999999998</v>
+      </c>
+      <c r="P138" s="5">
+        <v>23095.919999999998</v>
+      </c>
+      <c r="Q138" s="6">
+        <v>0.21547685896872504</v>
+      </c>
+      <c r="R138" s="7">
+        <v>213</v>
+      </c>
+      <c r="S138" s="6">
+        <v>0.22413793103448265</v>
+      </c>
+      <c r="T138" s="6">
+        <v>0.28689912330835926</v>
+      </c>
+      <c r="U138" s="6">
+        <v>0.006722364815950177</v>
+      </c>
+      <c r="V138" s="6">
+        <v>0.036312236100575344</v>
+      </c>
+      <c r="W138" s="6">
+        <v>0.012338304774176564</v>
+      </c>
+      <c r="X138" s="8">
+        <v>30.4562874251497</v>
+      </c>
+      <c r="Y138" s="6">
+        <v>0.67664670658682635</v>
+      </c>
+      <c r="Z138" s="6">
+        <v>0.10778443113772455</v>
+      </c>
+      <c r="AA138" s="8">
+        <v>9.3205256157635468</v>
+      </c>
+      <c r="AB138" s="8">
+        <v>7.3763213414634139</v>
+      </c>
+      <c r="AC138" s="8">
+        <v>16.424897999999999</v>
+      </c>
+      <c r="AD138" s="8">
+        <v>22.91207604790419</v>
+      </c>
+      <c r="AE138" s="6">
+        <v>0.48502994011976047</v>
+      </c>
       <c r="AF138" s="9"/>
-      <c r="AG138" s="5"/>
+      <c r="AG138" s="5">
+        <v>-382.10000000000002</v>
+      </c>
       <c r="AH138" s="10">
         <v>3</v>
       </c>
@@ -19271,7 +19829,9 @@
       <c r="AB146" s="8">
         <v>3.1479166666666667</v>
       </c>
-      <c r="AC146" s="8"/>
+      <c r="AC146" s="8">
+        <v>6.8761469999999996</v>
+      </c>
       <c r="AD146" s="8">
         <v>12.787152083333334</v>
       </c>
@@ -19507,16 +20067,16 @@
         <v>-0.15517241379310343</v>
       </c>
       <c r="T148" s="6">
-        <v>-0.001288800173067452</v>
+        <v>1.0121829206359922</v>
       </c>
       <c r="U148" s="6">
-        <v>-0.29440568667733508</v>
+        <v>0.71906603413172465</v>
       </c>
       <c r="V148" s="6">
         <v>0.016755207749985044</v>
       </c>
       <c r="W148" s="6">
-        <v>-0.0033861306689946897</v>
+        <v>0.00191022432794441</v>
       </c>
       <c r="X148" s="8">
         <v>37.511475409836059</v>
@@ -19664,7 +20224,9 @@
       <c r="AB149" s="8">
         <v>11.607802127659573</v>
       </c>
-      <c r="AC149" s="8"/>
+      <c r="AC149" s="8">
+        <v>19.928554999999999</v>
+      </c>
       <c r="AD149" s="8">
         <v>25.603594117647059</v>
       </c>
@@ -20864,7 +21426,9 @@
       <c r="AB159" s="8">
         <v>7.2327523255813952</v>
       </c>
-      <c r="AC159" s="8"/>
+      <c r="AC159" s="8">
+        <v>16.682366999999999</v>
+      </c>
       <c r="AD159" s="8">
         <v>23.629263953488373</v>
       </c>
@@ -20989,7 +21553,9 @@
       <c r="AB160" s="8">
         <v>10.829166071428572</v>
       </c>
-      <c r="AC160" s="8"/>
+      <c r="AC160" s="8">
+        <v>18.231504999999999</v>
+      </c>
       <c r="AD160" s="8">
         <v>24.939180701754388</v>
       </c>
@@ -21116,7 +21682,9 @@
       <c r="AB161" s="8">
         <v>6.1433400000000002</v>
       </c>
-      <c r="AC161" s="8"/>
+      <c r="AC161" s="8">
+        <v>10.916665999999999</v>
+      </c>
       <c r="AD161" s="8">
         <v>16.16</v>
       </c>
@@ -21167,7 +21735,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -21203,25 +21771,61 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
-      <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="O162" s="5">
+        <v>12855.799999999999</v>
+      </c>
+      <c r="P162" s="5">
+        <v>12855.799999999999</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>0.14832219620929865</v>
+      </c>
+      <c r="R162" s="7">
+        <v>120</v>
+      </c>
+      <c r="S162" s="6">
+        <v>-0.040000000000000036</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.25993003158107625</v>
+      </c>
+      <c r="U162" s="6">
+        <v>-0.021797282160581216</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.04681178923131972</v>
+      </c>
+      <c r="W162" s="6">
+        <v>0.03696409402759844</v>
+      </c>
+      <c r="X162" s="8">
+        <v>53.404166250000003</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0.84999999999999998</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>30.798275862068966</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>5.2160256410256416</v>
+      </c>
+      <c r="AC162" s="8">
+        <v>36.846857999999997</v>
+      </c>
+      <c r="AD162" s="8">
+        <v>44.548333749999998</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.025000000000000001</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>-525.88</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -21340,7 +21944,9 @@
       <c r="AB163" s="8">
         <v>14.332791056910569</v>
       </c>
-      <c r="AC163" s="8"/>
+      <c r="AC163" s="8">
+        <v>18.205271</v>
+      </c>
       <c r="AD163" s="8">
         <v>24.878974615384617</v>
       </c>
@@ -21879,7 +22485,7 @@
         <v>19883</v>
       </c>
       <c r="B168" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C168" s="4">
         <v>44</v>
@@ -21915,25 +22521,61 @@
       <c t="s" r="N168" s="4">
         <v>52</v>
       </c>
-      <c r="O168" s="5"/>
-      <c r="P168" s="5"/>
-      <c r="Q168" s="6"/>
-      <c r="R168" s="7"/>
-      <c r="S168" s="6"/>
-      <c r="T168" s="6"/>
-      <c r="U168" s="6"/>
-      <c r="V168" s="6"/>
-      <c r="W168" s="6"/>
-      <c r="X168" s="8"/>
-      <c r="Y168" s="6"/>
-      <c r="Z168" s="6"/>
-      <c r="AA168" s="8"/>
-      <c r="AB168" s="8"/>
-      <c r="AC168" s="8"/>
-      <c r="AD168" s="8"/>
-      <c r="AE168" s="6"/>
+      <c r="O168" s="5">
+        <v>7858</v>
+      </c>
+      <c r="P168" s="5">
+        <v>7858</v>
+      </c>
+      <c r="Q168" s="6">
+        <v>0.37287377528058463</v>
+      </c>
+      <c r="R168" s="7">
+        <v>83</v>
+      </c>
+      <c r="S168" s="6">
+        <v>0.20289855072463769</v>
+      </c>
+      <c r="T168" s="6">
+        <v>0.33640067447187577</v>
+      </c>
+      <c r="U168" s="6">
+        <v>-0.021065601934334436</v>
+      </c>
+      <c r="V168" s="6">
+        <v>0.045566492746245864</v>
+      </c>
+      <c r="W168" s="6">
+        <v>0.011011898701959786</v>
+      </c>
+      <c r="X168" s="8">
+        <v>24.677192982456138</v>
+      </c>
+      <c r="Y168" s="6">
+        <v>0.68421052631578949</v>
+      </c>
+      <c r="Z168" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA168" s="8">
+        <v>3.7335337349397593</v>
+      </c>
+      <c r="AB168" s="8">
+        <v>5.9548490909090912</v>
+      </c>
+      <c r="AC168" s="8">
+        <v>9.7477850000000004</v>
+      </c>
+      <c r="AD168" s="8">
+        <v>16.327485964912281</v>
+      </c>
+      <c r="AE168" s="6">
+        <v>0.82456140350877194</v>
+      </c>
       <c r="AF168" s="9"/>
-      <c r="AG168" s="5"/>
+      <c r="AG168" s="5">
+        <v>0</v>
+      </c>
       <c r="AH168" s="10">
         <v>5</v>
       </c>
@@ -21974,7 +22616,7 @@
         <v>19884</v>
       </c>
       <c r="B169" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C169" s="4">
         <v>44</v>
@@ -22010,25 +22652,61 @@
       <c t="s" r="N169" s="4">
         <v>52</v>
       </c>
-      <c r="O169" s="5"/>
-      <c r="P169" s="5"/>
-      <c r="Q169" s="6"/>
-      <c r="R169" s="7"/>
-      <c r="S169" s="6"/>
-      <c r="T169" s="6"/>
-      <c r="U169" s="6"/>
-      <c r="V169" s="6"/>
-      <c r="W169" s="6"/>
-      <c r="X169" s="8"/>
-      <c r="Y169" s="6"/>
-      <c r="Z169" s="6"/>
-      <c r="AA169" s="8"/>
-      <c r="AB169" s="8"/>
-      <c r="AC169" s="8"/>
-      <c r="AD169" s="8"/>
-      <c r="AE169" s="6"/>
+      <c r="O169" s="5">
+        <v>5265.6999999999998</v>
+      </c>
+      <c r="P169" s="5">
+        <v>5265.6999999999998</v>
+      </c>
+      <c r="Q169" s="6">
+        <v>-0.62391349374700922</v>
+      </c>
+      <c r="R169" s="7">
+        <v>55</v>
+      </c>
+      <c r="S169" s="6">
+        <v>-0.59558823529411764</v>
+      </c>
+      <c r="T169" s="6">
+        <v>0.29223235277361037</v>
+      </c>
+      <c r="U169" s="6">
+        <v>-0.013077482575915832</v>
+      </c>
+      <c r="V169" s="6">
+        <v>0.055236245893233574</v>
+      </c>
+      <c r="W169" s="6">
+        <v>0.024157756803463926</v>
+      </c>
+      <c r="X169" s="8">
+        <v>33.587499999999999</v>
+      </c>
+      <c r="Y169" s="6">
+        <v>0.26829268292682928</v>
+      </c>
+      <c r="Z169" s="6">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="AA169" s="8">
+        <v>6.7672833333333324</v>
+      </c>
+      <c r="AB169" s="8">
+        <v>7.9487179487179489</v>
+      </c>
+      <c r="AC169" s="8">
+        <v>15.139367</v>
+      </c>
+      <c r="AD169" s="8">
+        <v>21.546667500000002</v>
+      </c>
+      <c r="AE169" s="6">
+        <v>0.32500000000000001</v>
+      </c>
       <c r="AF169" s="9"/>
-      <c r="AG169" s="5"/>
+      <c r="AG169" s="5">
+        <v>0</v>
+      </c>
       <c r="AH169" s="10">
         <v>3</v>
       </c>
@@ -22540,7 +23218,9 @@
       <c r="AB173" s="8">
         <v>6.666666666666667</v>
       </c>
-      <c r="AC173" s="8"/>
+      <c r="AC173" s="8">
+        <v>10.664285</v>
+      </c>
       <c r="AD173" s="8">
         <v>14.20635</v>
       </c>
@@ -23187,7 +23867,9 @@
       <c r="AB178" s="8">
         <v>3.7169449999999999</v>
       </c>
-      <c r="AC178" s="8"/>
+      <c r="AC178" s="8">
+        <v>11.453332</v>
+      </c>
       <c r="AD178" s="8">
         <v>18.408888333333334</v>
       </c>
@@ -23314,7 +23996,9 @@
       <c r="AB179" s="8">
         <v>2.2209961038961037</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>7.1380939999999997</v>
+      </c>
       <c r="AD179" s="8">
         <v>14.083983116883116</v>
       </c>
@@ -23363,7 +24047,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>44</v>
@@ -23399,25 +24083,61 @@
       <c t="s" r="N180" s="4">
         <v>52</v>
       </c>
-      <c r="O180" s="5"/>
-      <c r="P180" s="5"/>
-      <c r="Q180" s="6"/>
-      <c r="R180" s="7"/>
-      <c r="S180" s="6"/>
-      <c r="T180" s="6"/>
-      <c r="U180" s="6"/>
-      <c r="V180" s="6"/>
-      <c r="W180" s="6"/>
-      <c r="X180" s="8"/>
-      <c r="Y180" s="6"/>
-      <c r="Z180" s="6"/>
-      <c r="AA180" s="8"/>
-      <c r="AB180" s="8"/>
-      <c r="AC180" s="8"/>
-      <c r="AD180" s="8"/>
-      <c r="AE180" s="6"/>
+      <c r="O180" s="5">
+        <v>4681.7700000000004</v>
+      </c>
+      <c r="P180" s="5">
+        <v>4681.7700000000004</v>
+      </c>
+      <c r="Q180" s="6">
+        <v>-0.3380860954492243</v>
+      </c>
+      <c r="R180" s="7">
+        <v>50</v>
+      </c>
+      <c r="S180" s="6">
+        <v>-0.39759036144578308</v>
+      </c>
+      <c r="T180" s="6">
+        <v>0</v>
+      </c>
+      <c r="U180" s="6">
+        <v>-0.29677451049496234</v>
+      </c>
+      <c r="V180" s="6">
+        <v>0.014262127357815527</v>
+      </c>
+      <c r="W180" s="6">
+        <v>-0.031421449579966551</v>
+      </c>
+      <c r="X180" s="8">
+        <v>36.80175263157895</v>
+      </c>
+      <c r="Y180" s="6">
+        <v>0.26315789473684209</v>
+      </c>
+      <c r="Z180" s="6">
+        <v>0.26315789473684209</v>
+      </c>
+      <c r="AA180" s="8">
+        <v>8.4113340000000001</v>
+      </c>
+      <c r="AB180" s="8">
+        <v>15.252941176470589</v>
+      </c>
+      <c r="AC180" s="8">
+        <v>26.231888000000001</v>
+      </c>
+      <c r="AD180" s="8">
+        <v>32.30175263157895</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>0.21052631578947367</v>
+      </c>
       <c r="AF180" s="9"/>
-      <c r="AG180" s="5"/>
+      <c r="AG180" s="5">
+        <v>0</v>
+      </c>
       <c r="AH180" s="10">
         <v>2</v>
       </c>
@@ -23458,7 +24178,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -23494,25 +24214,61 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
-      <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="O181" s="5">
+        <v>5615.8000000000002</v>
+      </c>
+      <c r="P181" s="5">
+        <v>5615.8000000000002</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>0.16988521550736402</v>
+      </c>
+      <c r="R181" s="7">
+        <v>54</v>
+      </c>
+      <c r="S181" s="6">
+        <v>0.018867924528301883</v>
+      </c>
+      <c r="T181" s="6">
+        <v>-0.055199615370917769</v>
+      </c>
+      <c r="U181" s="6">
+        <v>-0.30711207664090601</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.061066544392606573</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.037716353858755651</v>
+      </c>
+      <c r="X181" s="8">
+        <v>15.069190909090908</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>0.87878787878787878</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>3.3817907407407408</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>2.6320538461538465</v>
+      </c>
+      <c r="AC181" s="8">
+        <v>5.9972019999999997</v>
+      </c>
+      <c r="AD181" s="8">
+        <v>10.373233333333333</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>1</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>
@@ -23614,7 +24370,7 @@
         <v>0.042347812045858226</v>
       </c>
       <c r="W182" s="6">
-        <v>0.026730179234619733</v>
+        <v>0.0265803326336186</v>
       </c>
       <c r="X182" s="8">
         <v>21.459401282051282</v>
@@ -23762,7 +24518,9 @@
       <c r="AB183" s="8">
         <v>3.5385177777777779</v>
       </c>
-      <c r="AC183" s="8"/>
+      <c r="AC183" s="8">
+        <v>8.3497420000000009</v>
+      </c>
       <c r="AD183" s="8">
         <v>15.856463265306122</v>
       </c>
@@ -23908,7 +24666,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -24132,7 +24890,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -24168,25 +24926,61 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
-      <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="O187" s="5">
+        <v>2523.5999999999999</v>
+      </c>
+      <c r="P187" s="5">
+        <v>2523.5999999999999</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>0.13454388512495896</v>
+      </c>
+      <c r="R187" s="7">
+        <v>31</v>
+      </c>
+      <c r="S187" s="6">
+        <v>0.19230769230769229</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.31419797115232206</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.13357049453162151</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.086819820890790933</v>
+      </c>
+      <c r="X187" s="8">
+        <v>23.118839130434782</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>3.7010741935483873</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>3.5355086956521737</v>
+      </c>
+      <c r="AC187" s="8">
+        <v>6.7862309999999999</v>
+      </c>
+      <c r="AD187" s="8">
+        <v>13.755073913043477</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.95652173913043481</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>-133.69999999999999</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -24360,7 +25154,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -24396,25 +25190,61 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
-      <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="O189" s="5">
+        <v>6505.96</v>
+      </c>
+      <c r="P189" s="5">
+        <v>6505.96</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.074528755299593241</v>
+      </c>
+      <c r="R189" s="7">
+        <v>83</v>
+      </c>
+      <c r="S189" s="6">
+        <v>0</v>
+      </c>
+      <c r="T189" s="6">
+        <v>0.25367194080504646</v>
+      </c>
+      <c r="U189" s="6">
+        <v>-0.039262537734631016</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.068521094504116226</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.041697996913599225</v>
+      </c>
+      <c r="X189" s="8">
+        <v>31.105250684931509</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.054794520547945202</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.20547945205479451</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>6.8172686746987949</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>12.039285714285715</v>
+      </c>
+      <c r="AC189" s="8">
+        <v>18.828326000000001</v>
+      </c>
+      <c r="AD189" s="8">
+        <v>25.090867123287669</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.47945205479452052</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>-59.799999999999997</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -24455,7 +25285,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -24491,25 +25321,61 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
-      <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="O190" s="5">
+        <v>8016.6300000000001</v>
+      </c>
+      <c r="P190" s="5">
+        <v>8016.6300000000001</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>-0.053431572235702496</v>
+      </c>
+      <c r="R190" s="7">
+        <v>81</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.15625</v>
+      </c>
+      <c r="T190" s="6">
+        <v>0.18393951074204498</v>
+      </c>
+      <c r="U190" s="6">
+        <v>-0.102779472172222</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.061067056855561505</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.042489425107557668</v>
+      </c>
+      <c r="X190" s="8">
+        <v>23.441667500000001</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>0.65000000000000002</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>4.5415641975308638</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>5.192735897435897</v>
+      </c>
+      <c r="AC190" s="8">
+        <v>9.6794010000000004</v>
+      </c>
+      <c r="AD190" s="8">
+        <v>16.292917499999998</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.875</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>-231.84999999999999</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -24771,7 +25637,7 @@
         <v>0</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -25334,7 +26200,7 @@
         <v>19947</v>
       </c>
       <c r="B197" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C197" s="4">
         <v>44</v>
@@ -25370,25 +26236,61 @@
       <c t="s" r="N197" s="4">
         <v>52</v>
       </c>
-      <c r="O197" s="5"/>
-      <c r="P197" s="5"/>
-      <c r="Q197" s="6"/>
-      <c r="R197" s="7"/>
-      <c r="S197" s="6"/>
-      <c r="T197" s="6"/>
-      <c r="U197" s="6"/>
-      <c r="V197" s="6"/>
-      <c r="W197" s="6"/>
-      <c r="X197" s="8"/>
-      <c r="Y197" s="6"/>
-      <c r="Z197" s="6"/>
-      <c r="AA197" s="8"/>
-      <c r="AB197" s="8"/>
-      <c r="AC197" s="8"/>
-      <c r="AD197" s="8"/>
-      <c r="AE197" s="6"/>
+      <c r="O197" s="5">
+        <v>12560.6</v>
+      </c>
+      <c r="P197" s="5">
+        <v>12560.6</v>
+      </c>
+      <c r="Q197" s="6">
+        <v>-0.01960003777793895</v>
+      </c>
+      <c r="R197" s="7">
+        <v>121</v>
+      </c>
+      <c r="S197" s="6">
+        <v>-0.076335877862595436</v>
+      </c>
+      <c r="T197" s="6">
+        <v>0.35497866343964457</v>
+      </c>
+      <c r="U197" s="6">
+        <v>0.019434183080426094</v>
+      </c>
+      <c r="V197" s="6">
+        <v>0.036547497731000106</v>
+      </c>
+      <c r="W197" s="6">
+        <v>0.020576126936611309</v>
+      </c>
+      <c r="X197" s="8">
+        <v>20.462719736842104</v>
+      </c>
+      <c r="Y197" s="6">
+        <v>0.76315789473684215</v>
+      </c>
+      <c r="Z197" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA197" s="8">
+        <v>2.2957627118644064</v>
+      </c>
+      <c r="AB197" s="8">
+        <v>5.126577027027027</v>
+      </c>
+      <c r="AC197" s="8">
+        <v>7.3919259999999998</v>
+      </c>
+      <c r="AD197" s="8">
+        <v>14.091885526315791</v>
+      </c>
+      <c r="AE197" s="6">
+        <v>0.98684210526315785</v>
+      </c>
       <c r="AF197" s="9"/>
-      <c r="AG197" s="5"/>
+      <c r="AG197" s="5">
+        <v>-645.13</v>
+      </c>
       <c r="AH197" s="10">
         <v>5</v>
       </c>
@@ -25507,7 +26409,9 @@
       <c r="AB198" s="8">
         <v>3.8218749999999999</v>
       </c>
-      <c r="AC198" s="8"/>
+      <c r="AC198" s="8">
+        <v>11.71011</v>
+      </c>
       <c r="AD198" s="8">
         <v>18.722918750000002</v>
       </c>
@@ -25558,7 +26462,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>44</v>
@@ -25594,25 +26498,61 @@
       <c t="s" r="N199" s="4">
         <v>52</v>
       </c>
-      <c r="O199" s="5"/>
-      <c r="P199" s="5"/>
-      <c r="Q199" s="6"/>
-      <c r="R199" s="7"/>
-      <c r="S199" s="6"/>
-      <c r="T199" s="6"/>
-      <c r="U199" s="6"/>
-      <c r="V199" s="6"/>
-      <c r="W199" s="6"/>
-      <c r="X199" s="8"/>
-      <c r="Y199" s="6"/>
-      <c r="Z199" s="6"/>
-      <c r="AA199" s="8"/>
-      <c r="AB199" s="8"/>
-      <c r="AC199" s="8"/>
-      <c r="AD199" s="8"/>
-      <c r="AE199" s="6"/>
+      <c r="O199" s="5">
+        <v>6033.8800000000001</v>
+      </c>
+      <c r="P199" s="5">
+        <v>6033.8800000000001</v>
+      </c>
+      <c r="Q199" s="6">
+        <v>-0.17370143653369485</v>
+      </c>
+      <c r="R199" s="7">
+        <v>69</v>
+      </c>
+      <c r="S199" s="6">
+        <v>-0.23333333333333328</v>
+      </c>
+      <c r="T199" s="6">
+        <v>0.31385436899640035</v>
+      </c>
+      <c r="U199" s="6">
+        <v>-0.049323221542357493</v>
+      </c>
+      <c r="V199" s="6">
+        <v>0.010126320046139465</v>
+      </c>
+      <c r="W199" s="6">
+        <v>-0.013341166877697269</v>
+      </c>
+      <c r="X199" s="8">
+        <v>36.457499999999996</v>
+      </c>
+      <c r="Y199" s="6">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="Z199" s="6">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="AA199" s="8">
+        <v>4.8325985294117642</v>
+      </c>
+      <c r="AB199" s="8">
+        <v>14.882479487179486</v>
+      </c>
+      <c r="AC199" s="8">
+        <v>20.141604000000001</v>
+      </c>
+      <c r="AD199" s="8">
+        <v>26.77375</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>0.32500000000000001</v>
+      </c>
       <c r="AF199" s="9"/>
-      <c r="AG199" s="5"/>
+      <c r="AG199" s="5">
+        <v>-374.63</v>
+      </c>
       <c r="AH199" s="10">
         <v>1</v>
       </c>
@@ -25653,7 +26593,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -25689,25 +26629,61 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
-      <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="O200" s="5">
+        <v>3722.77</v>
+      </c>
+      <c r="P200" s="5">
+        <v>3722.77</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>-0.014790957641068525</v>
+      </c>
+      <c r="R200" s="7">
+        <v>48</v>
+      </c>
+      <c r="S200" s="6">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="T200" s="6">
+        <v>0</v>
+      </c>
+      <c r="U200" s="6">
+        <v>-0.38623659264472421</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.08637318448359689</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.050630981768951616</v>
+      </c>
+      <c r="X200" s="8">
+        <v>30.758695652173916</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>0.65217391304347827</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>10.117000000000001</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>4.078335</v>
+      </c>
+      <c r="AC200" s="8">
+        <v>15.836333</v>
+      </c>
+      <c r="AD200" s="8">
+        <v>20.412317391304349</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0.56521739130434778</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>-76.900000000000006</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -25919,7 +26895,9 @@
       <c r="AB202" s="8">
         <v>8.65245</v>
       </c>
-      <c r="AC202" s="8"/>
+      <c r="AC202" s="8">
+        <v>14.013724</v>
+      </c>
       <c r="AD202" s="8">
         <v>20.914214705882355</v>
       </c>
@@ -25970,7 +26948,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -26194,7 +27172,7 @@
         <v>19959</v>
       </c>
       <c r="B205" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C205" s="4">
         <v>44</v>
@@ -26230,25 +27208,57 @@
       <c t="s" r="N205" s="4">
         <v>52</v>
       </c>
-      <c r="O205" s="5"/>
-      <c r="P205" s="5"/>
+      <c r="O205" s="5">
+        <v>6184.9399999999996</v>
+      </c>
+      <c r="P205" s="5">
+        <v>6184.9399999999996</v>
+      </c>
       <c r="Q205" s="6"/>
-      <c r="R205" s="7"/>
+      <c r="R205" s="7">
+        <v>82</v>
+      </c>
       <c r="S205" s="6"/>
-      <c r="T205" s="6"/>
-      <c r="U205" s="6"/>
-      <c r="V205" s="6"/>
-      <c r="W205" s="6"/>
-      <c r="X205" s="8"/>
-      <c r="Y205" s="6"/>
-      <c r="Z205" s="6"/>
-      <c r="AA205" s="8"/>
-      <c r="AB205" s="8"/>
-      <c r="AC205" s="8"/>
-      <c r="AD205" s="8"/>
-      <c r="AE205" s="6"/>
+      <c r="T205" s="6">
+        <v>0.16521815894737865</v>
+      </c>
+      <c r="U205" s="6">
+        <v>-0.20500693620309979</v>
+      </c>
+      <c r="V205" s="6">
+        <v>0.014367398875332666</v>
+      </c>
+      <c r="W205" s="6">
+        <v>-0.010840606376132995</v>
+      </c>
+      <c r="X205" s="8">
+        <v>32.603203846153846</v>
+      </c>
+      <c r="Y205" s="6">
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="Z205" s="6">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="AA205" s="8">
+        <v>9.8170837500000001</v>
+      </c>
+      <c r="AB205" s="8">
+        <v>7.5076923076923077</v>
+      </c>
+      <c r="AC205" s="8">
+        <v>16.243185</v>
+      </c>
+      <c r="AD205" s="8">
+        <v>23.008973076923077</v>
+      </c>
+      <c r="AE205" s="6">
+        <v>0.46153846153846156</v>
+      </c>
       <c r="AF205" s="9"/>
-      <c r="AG205" s="5"/>
+      <c r="AG205" s="5">
+        <v>-730.78999999999996</v>
+      </c>
       <c r="AH205" s="10">
         <v>3</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-17).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-17).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-170</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 1.719.893,36</t>
-  </si>
-  <si>
-    <t>R$ 9.347,25
-R$ 9.586,69</t>
+176</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>R$ 1.770.235,34</t>
+  </si>
+  <si>
+    <t>R$ 9.317,03
+R$ 9.545,90</t>
   </si>
   <si>
     <t>(7.5%)
-(5.1%)</t>
-  </si>
-  <si>
-    <t>98.4</t>
-  </si>
-  <si>
-    <t>(10.2%)</t>
-  </si>
-  <si>
-    <t>59.1%</t>
-  </si>
-  <si>
-    <t>17.6%</t>
+(5.6%)</t>
+  </si>
+  <si>
+    <t>97.4</t>
+  </si>
+  <si>
+    <t>(10.8%)</t>
+  </si>
+  <si>
+    <t>58.1%</t>
+  </si>
+  <si>
+    <t>16.9%</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,16 +950,16 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>28.0</t>
+    <t>28.1</t>
   </si>
   <si>
     <t>62.7%</t>
   </si>
   <si>
-    <t>12.4%</t>
-  </si>
-  <si>
-    <t>6.0</t>
+    <t>12.3%</t>
+  </si>
+  <si>
+    <t>6.1</t>
   </si>
   <si>
     <t>6.9</t>
@@ -971,10 +971,10 @@
     <t>19.8</t>
   </si>
   <si>
-    <t>67.1%</t>
-  </si>
-  <si>
-    <t>-R$ 38.719,44</t>
+    <t>66.9%</t>
+  </si>
+  <si>
+    <t>-R$ 38.899,34</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2069,7 +2069,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2105,25 +2105,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>13752.48</v>
+      </c>
+      <c r="P6" s="5">
+        <v>13752.48</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.0017737302895588503</v>
+      </c>
+      <c r="R6" s="7">
+        <v>134</v>
+      </c>
+      <c r="S6" s="6">
+        <v>-0.11258278145695366</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.26530113841285358</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.007795786650844066</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.028004592626202696</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0049949245517899319</v>
+      </c>
+      <c r="X6" s="8">
+        <v>26.357446808510637</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0.063829787234042548</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>10.242692307692307</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.8046095744680852</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>13.196275</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>20.153545744680851</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.69148936170212771</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>-116.90000000000001</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -7882,7 +7918,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7918,25 +7954,51 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
+      <c r="O51" s="5">
+        <v>0</v>
+      </c>
+      <c r="P51" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R51" s="7">
+        <v>9</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.64000000000000001</v>
+      </c>
       <c r="T51" s="6"/>
       <c r="U51" s="6"/>
       <c r="V51" s="6"/>
       <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="X51" s="8">
+        <v>33.90334</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>4.3685222222222215</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>19.443339999999999</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>31.330000000000002</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8809,7 +8871,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>11.792111999999999</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -14233,7 +14297,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14269,25 +14333,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>7441.5100000000002</v>
+      </c>
+      <c r="P102" s="5">
+        <v>7441.5100000000002</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.09773631116930992</v>
+      </c>
+      <c r="R102" s="7">
+        <v>72</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.18181818181818177</v>
+      </c>
+      <c r="T102" s="6">
+        <v>-1.695892365931108E-05</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.35465197251633068</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.012897382386101745</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.0014316986740594314</v>
+      </c>
+      <c r="X102" s="8">
+        <v>42.854761224489792</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.12244897959183673</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.51020408163265307</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>12.872916666666667</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>9.401020408163264</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>22.307482</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>29.203061224489797</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.18367346938775511</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -20408,7 +20508,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20444,25 +20544,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>7620.1400000000003</v>
+      </c>
+      <c r="P151" s="5">
+        <v>7620.1400000000003</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.25654849712381267</v>
+      </c>
+      <c r="R151" s="7">
+        <v>74</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.32727272727272727</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.24706364974921718</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.048848236384108422</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.033699905776009363</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.012171429921235042</v>
+      </c>
+      <c r="X151" s="8">
+        <v>30.91293103448276</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.31034482758620691</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>9.0317567567567565</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>3.6479526315789474</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>12.159447</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>18.987643103448278</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.55172413793103448</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21158,7 +21294,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21194,25 +21330,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>6601.1700000000001</v>
+      </c>
+      <c r="P157" s="5">
+        <v>6601.1700000000001</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>-0.14924386339793638</v>
+      </c>
+      <c r="R157" s="7">
+        <v>63</v>
+      </c>
+      <c r="S157" s="6">
+        <v>-0.24096385542168675</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.33385377137689226</v>
+      </c>
+      <c r="U157" s="6">
+        <v>0.012288048936779388</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.044357363921850218</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.024679034171215104</v>
+      </c>
+      <c r="X157" s="8">
+        <v>27.279320370370371</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.49090909090909091</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0.018518518518518517</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>5.1320111111111117</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>3.6433962264150943</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>8.8285470000000004</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>15.67962962962963</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.70370370370370372</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21253,7 +21425,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21289,25 +21461,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>7301.3199999999997</v>
+      </c>
+      <c r="P158" s="5">
+        <v>7301.3199999999997</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.33748374633300038</v>
+      </c>
+      <c r="R158" s="7">
+        <v>71</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.34259259259259256</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.29387016320336601</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.016521683750335556</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.027681980792514233</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.0064597908323426453</v>
+      </c>
+      <c r="X158" s="8">
+        <v>30.435555000000001</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>6.6390471428571427</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>5.0125000000000002</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>11.816666</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>18.771111666666666</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.53333333333333333</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22128,7 +22336,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22164,25 +22372,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>7625.3599999999997</v>
+      </c>
+      <c r="P165" s="5">
+        <v>7625.3599999999997</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>-0.30764523328303217</v>
+      </c>
+      <c r="R165" s="7">
+        <v>71</v>
+      </c>
+      <c r="S165" s="6">
+        <v>-0.4453125</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.30616073208346883</v>
+      </c>
+      <c r="U165" s="6">
+        <v>1.9120408741357787E-05</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.023910543239925725</v>
+      </c>
+      <c r="W165" s="6">
+        <v>0.0019928895160359643</v>
+      </c>
+      <c r="X165" s="8">
+        <v>20.924073333333332</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>6.1997647887323941</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>1.7685177777777776</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>7.5601839999999996</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>14.575184444444444</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>-63.799999999999997</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
